--- a/templates/excel/eu-ai-act-mapping.xlsx
+++ b/templates/excel/eu-ai-act-mapping.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Article_Obligations" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Evidence_Trail" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Audit_Log_Index" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="README" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="_metadata" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet name="_metadata" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="README" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -989,143 +989,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># eu-ai-act-mapping.xlsx</t>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>spec_version</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PURPOSE</t>
+          <t>generation_date</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Compliance register for EU-operating organisations per governance/EU-AI-ACT.md. MANDATORY for EU adopters from 2 August 2026.</t>
+          <t>oot_version</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>WRITTEN BY</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>- Skill Pack S7 (Governance &amp; Compliance) at use-case classification time.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>- Routine R6 (daily 23:00) — appends Audit_Log_Index row.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>- Manual + counsel review for Annex_III_Risk_Mapping.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>READ BY</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>- Skill Pack S7 at all times.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>- Counsel — annual review minimum.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>- Routine R2 (Weekly BR) — anomaly count surfaces in KPI block.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>NOTE: this document is methodology, not legal advice. Counsel review is mandatory for EU adopters before relying on any classification herein.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>DO NOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>- Treat compliance as a one-time exercise; it is continuous.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>- Bypass the daily R6 audit trail.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>- Claim EU AI Act compliance without counsel review.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>- Modify a use case's Annex III classification without re-running counsel review.</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>file_id</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>X7</t>
         </is>
       </c>
     </row>
@@ -1140,66 +1063,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>value</t>
+          <t># eu-ai-act-mapping.xlsx</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>spec_version</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1.0.0</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>generation_date</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
+          <t>PURPOSE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>oot_version</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1.0.0</t>
+          <t>Compliance register for EU-operating organisations per governance/EU-AI-ACT.md. MANDATORY for EU adopters from 2 August 2026.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>file_id</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>X7</t>
+      <c r="A5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WRITTEN BY</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>- Skill Pack S7 (Governance &amp; Compliance) at use-case classification time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>- Routine R6 (daily 23:00) — appends Audit_Log_Index row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>- Manual + counsel review for Annex_III_Risk_Mapping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>READ BY</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>- Skill Pack S7 at all times.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>- Counsel — annual review minimum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>- Routine R2 (Weekly BR) — anomaly count surfaces in KPI block.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NOTE: this document is methodology, not legal advice. Counsel review is mandatory for EU adopters before relying on any classification herein.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>DO NOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>- Treat compliance as a one-time exercise; it is continuous.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>- Bypass the daily R6 audit trail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>- Claim EU AI Act compliance without counsel review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>- Modify a use case's Annex III classification without re-running counsel review.</t>
         </is>
       </c>
     </row>
